--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815764</v>
+        <v>119815610</v>
       </c>
       <c r="B2" t="n">
-        <v>79642</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459148</v>
+        <v>458934</v>
       </c>
       <c r="R2" t="n">
-        <v>7073462</v>
+        <v>7073666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815337</v>
+        <v>119815635</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458974</v>
+        <v>459066</v>
       </c>
       <c r="R4" t="n">
-        <v>7073639</v>
+        <v>7073606</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815638</v>
+        <v>119815375</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>97928</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459085</v>
+        <v>458705</v>
       </c>
       <c r="R5" t="n">
-        <v>7073606</v>
+        <v>7073870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815610</v>
+        <v>119815766</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>79642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458934</v>
+        <v>458974</v>
       </c>
       <c r="R6" t="n">
-        <v>7073666</v>
+        <v>7073639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815472</v>
+        <v>119815247</v>
       </c>
       <c r="B7" t="n">
-        <v>79635</v>
+        <v>74638</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458907</v>
+        <v>458953</v>
       </c>
       <c r="R7" t="n">
-        <v>7073661</v>
+        <v>7073657</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815247</v>
+        <v>119815638</v>
       </c>
       <c r="B8" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458953</v>
+        <v>459085</v>
       </c>
       <c r="R8" t="n">
-        <v>7073657</v>
+        <v>7073606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815635</v>
+        <v>119815764</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,20 +1429,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459066</v>
+        <v>459148</v>
       </c>
       <c r="R9" t="n">
-        <v>7073606</v>
+        <v>7073462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815375</v>
+        <v>119815340</v>
       </c>
       <c r="B10" t="n">
-        <v>97928</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458705</v>
+        <v>459110</v>
       </c>
       <c r="R10" t="n">
-        <v>7073870</v>
+        <v>7073509</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815766</v>
+        <v>119815535</v>
       </c>
       <c r="B11" t="n">
-        <v>79642</v>
+        <v>93935</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458974</v>
+        <v>458953</v>
       </c>
       <c r="R11" t="n">
-        <v>7073639</v>
+        <v>7073651</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815340</v>
+        <v>119815472</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459110</v>
+        <v>458907</v>
       </c>
       <c r="R12" t="n">
-        <v>7073509</v>
+        <v>7073661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815535</v>
+        <v>119815337</v>
       </c>
       <c r="B13" t="n">
-        <v>93935</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2387</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458953</v>
+        <v>458974</v>
       </c>
       <c r="R13" t="n">
-        <v>7073651</v>
+        <v>7073639</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815535</v>
+        <v>119815472</v>
       </c>
       <c r="B11" t="n">
-        <v>93935</v>
+        <v>79635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458953</v>
+        <v>458907</v>
       </c>
       <c r="R11" t="n">
-        <v>7073651</v>
+        <v>7073661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815472</v>
+        <v>119815535</v>
       </c>
       <c r="B12" t="n">
-        <v>79635</v>
+        <v>93935</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>2387</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458907</v>
+        <v>458953</v>
       </c>
       <c r="R12" t="n">
-        <v>7073661</v>
+        <v>7073651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815610</v>
+        <v>119815766</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>79642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458934</v>
+        <v>458974</v>
       </c>
       <c r="R2" t="n">
-        <v>7073666</v>
+        <v>7073639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815642</v>
+        <v>119815610</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458927</v>
+        <v>458934</v>
       </c>
       <c r="R3" t="n">
-        <v>7073670</v>
+        <v>7073666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815635</v>
+        <v>119815638</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459066</v>
+        <v>459085</v>
       </c>
       <c r="R4" t="n">
         <v>7073606</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815375</v>
+        <v>119815472</v>
       </c>
       <c r="B5" t="n">
-        <v>97928</v>
+        <v>79635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458705</v>
+        <v>458907</v>
       </c>
       <c r="R5" t="n">
-        <v>7073870</v>
+        <v>7073661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815766</v>
+        <v>119815337</v>
       </c>
       <c r="B6" t="n">
-        <v>79642</v>
+        <v>79636</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815247</v>
+        <v>119815535</v>
       </c>
       <c r="B7" t="n">
-        <v>74638</v>
+        <v>93935</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
         <v>458953</v>
       </c>
       <c r="R7" t="n">
-        <v>7073657</v>
+        <v>7073651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815638</v>
+        <v>119815642</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459085</v>
+        <v>458927</v>
       </c>
       <c r="R8" t="n">
-        <v>7073606</v>
+        <v>7073670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815340</v>
+        <v>119815247</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>74638</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459110</v>
+        <v>458953</v>
       </c>
       <c r="R10" t="n">
-        <v>7073509</v>
+        <v>7073657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815472</v>
+        <v>119815635</v>
       </c>
       <c r="B11" t="n">
-        <v>79635</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458907</v>
+        <v>459066</v>
       </c>
       <c r="R11" t="n">
-        <v>7073661</v>
+        <v>7073606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815535</v>
+        <v>119815375</v>
       </c>
       <c r="B12" t="n">
-        <v>93935</v>
+        <v>97928</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2387</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458953</v>
+        <v>458705</v>
       </c>
       <c r="R12" t="n">
-        <v>7073651</v>
+        <v>7073870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815337</v>
+        <v>119815340</v>
       </c>
       <c r="B13" t="n">
         <v>79636</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458974</v>
+        <v>459110</v>
       </c>
       <c r="R13" t="n">
-        <v>7073639</v>
+        <v>7073509</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815766</v>
+        <v>119815247</v>
       </c>
       <c r="B2" t="n">
-        <v>79642</v>
+        <v>74638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458974</v>
+        <v>458953</v>
       </c>
       <c r="R2" t="n">
-        <v>7073639</v>
+        <v>7073657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815610</v>
+        <v>119815766</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>79642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458934</v>
+        <v>458974</v>
       </c>
       <c r="R3" t="n">
-        <v>7073666</v>
+        <v>7073639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815638</v>
+        <v>119815340</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459085</v>
+        <v>459110</v>
       </c>
       <c r="R4" t="n">
-        <v>7073606</v>
+        <v>7073509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815472</v>
+        <v>119815764</v>
       </c>
       <c r="B5" t="n">
-        <v>79635</v>
+        <v>79642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458907</v>
+        <v>459148</v>
       </c>
       <c r="R5" t="n">
-        <v>7073661</v>
+        <v>7073462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815337</v>
+        <v>119815535</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>93935</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458974</v>
+        <v>458953</v>
       </c>
       <c r="R6" t="n">
-        <v>7073639</v>
+        <v>7073651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815535</v>
+        <v>119815375</v>
       </c>
       <c r="B7" t="n">
-        <v>93935</v>
+        <v>97928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2387</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458953</v>
+        <v>458705</v>
       </c>
       <c r="R7" t="n">
-        <v>7073651</v>
+        <v>7073870</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815642</v>
+        <v>119815635</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458927</v>
+        <v>459066</v>
       </c>
       <c r="R8" t="n">
-        <v>7073670</v>
+        <v>7073606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815764</v>
+        <v>119815638</v>
       </c>
       <c r="B9" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,20 +1429,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459148</v>
+        <v>459085</v>
       </c>
       <c r="R9" t="n">
-        <v>7073462</v>
+        <v>7073606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815247</v>
+        <v>119815337</v>
       </c>
       <c r="B10" t="n">
-        <v>74638</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458953</v>
+        <v>458974</v>
       </c>
       <c r="R10" t="n">
-        <v>7073657</v>
+        <v>7073639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815635</v>
+        <v>119815642</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459066</v>
+        <v>458927</v>
       </c>
       <c r="R11" t="n">
-        <v>7073606</v>
+        <v>7073670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815375</v>
+        <v>119815472</v>
       </c>
       <c r="B12" t="n">
-        <v>97928</v>
+        <v>79635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458705</v>
+        <v>458907</v>
       </c>
       <c r="R12" t="n">
-        <v>7073870</v>
+        <v>7073661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815340</v>
+        <v>119815610</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459110</v>
+        <v>458934</v>
       </c>
       <c r="R13" t="n">
-        <v>7073509</v>
+        <v>7073666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815340</v>
+        <v>119815535</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>93935</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459110</v>
+        <v>458953</v>
       </c>
       <c r="R4" t="n">
-        <v>7073509</v>
+        <v>7073651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815764</v>
+        <v>119815340</v>
       </c>
       <c r="B5" t="n">
-        <v>79642</v>
+        <v>79636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459148</v>
+        <v>459110</v>
       </c>
       <c r="R5" t="n">
-        <v>7073462</v>
+        <v>7073509</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815535</v>
+        <v>119815764</v>
       </c>
       <c r="B6" t="n">
-        <v>93935</v>
+        <v>79642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458953</v>
+        <v>459148</v>
       </c>
       <c r="R6" t="n">
-        <v>7073651</v>
+        <v>7073462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815535</v>
+        <v>119815340</v>
       </c>
       <c r="B4" t="n">
-        <v>93935</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458953</v>
+        <v>459110</v>
       </c>
       <c r="R4" t="n">
-        <v>7073651</v>
+        <v>7073509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815340</v>
+        <v>119815764</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459110</v>
+        <v>459148</v>
       </c>
       <c r="R5" t="n">
-        <v>7073509</v>
+        <v>7073462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815764</v>
+        <v>119815535</v>
       </c>
       <c r="B6" t="n">
-        <v>79642</v>
+        <v>93935</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459148</v>
+        <v>458953</v>
       </c>
       <c r="R6" t="n">
-        <v>7073462</v>
+        <v>7073651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815247</v>
+        <v>119815642</v>
       </c>
       <c r="B2" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458953</v>
+        <v>458927</v>
       </c>
       <c r="R2" t="n">
-        <v>7073657</v>
+        <v>7073670</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815766</v>
+        <v>119815535</v>
       </c>
       <c r="B3" t="n">
-        <v>79642</v>
+        <v>93958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458974</v>
+        <v>458953</v>
       </c>
       <c r="R3" t="n">
-        <v>7073639</v>
+        <v>7073651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815535</v>
+        <v>119815472</v>
       </c>
       <c r="B4" t="n">
-        <v>93935</v>
+        <v>79651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458953</v>
+        <v>458907</v>
       </c>
       <c r="R4" t="n">
-        <v>7073651</v>
+        <v>7073661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815340</v>
+        <v>119815610</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459110</v>
+        <v>458934</v>
       </c>
       <c r="R5" t="n">
-        <v>7073509</v>
+        <v>7073666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815764</v>
+        <v>119815375</v>
       </c>
       <c r="B6" t="n">
-        <v>79642</v>
+        <v>97951</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459148</v>
+        <v>458705</v>
       </c>
       <c r="R6" t="n">
-        <v>7073462</v>
+        <v>7073870</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815375</v>
+        <v>119815638</v>
       </c>
       <c r="B7" t="n">
-        <v>97928</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458705</v>
+        <v>459085</v>
       </c>
       <c r="R7" t="n">
-        <v>7073870</v>
+        <v>7073606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815635</v>
+        <v>119815340</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>79652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459066</v>
+        <v>459110</v>
       </c>
       <c r="R8" t="n">
-        <v>7073606</v>
+        <v>7073509</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815638</v>
+        <v>119815635</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459085</v>
+        <v>459066</v>
       </c>
       <c r="R9" t="n">
         <v>7073606</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815337</v>
+        <v>119815764</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79658</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458974</v>
+        <v>459148</v>
       </c>
       <c r="R10" t="n">
-        <v>7073639</v>
+        <v>7073462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815642</v>
+        <v>119815766</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79658</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458927</v>
+        <v>458974</v>
       </c>
       <c r="R11" t="n">
-        <v>7073670</v>
+        <v>7073639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815472</v>
+        <v>119815247</v>
       </c>
       <c r="B12" t="n">
-        <v>79635</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458907</v>
+        <v>458953</v>
       </c>
       <c r="R12" t="n">
-        <v>7073661</v>
+        <v>7073657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815610</v>
+        <v>119815337</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458934</v>
+        <v>458974</v>
       </c>
       <c r="R13" t="n">
-        <v>7073666</v>
+        <v>7073639</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815642</v>
+        <v>119815766</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458927</v>
+        <v>458974</v>
       </c>
       <c r="R2" t="n">
-        <v>7073670</v>
+        <v>7073639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815535</v>
+        <v>119815340</v>
       </c>
       <c r="B3" t="n">
-        <v>93958</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2387</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458953</v>
+        <v>459110</v>
       </c>
       <c r="R3" t="n">
-        <v>7073651</v>
+        <v>7073509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815472</v>
+        <v>119815337</v>
       </c>
       <c r="B4" t="n">
-        <v>79651</v>
+        <v>79652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458907</v>
+        <v>458974</v>
       </c>
       <c r="R4" t="n">
-        <v>7073661</v>
+        <v>7073639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815610</v>
+        <v>119815638</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458934</v>
+        <v>459085</v>
       </c>
       <c r="R5" t="n">
-        <v>7073666</v>
+        <v>7073606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815375</v>
+        <v>119815635</v>
       </c>
       <c r="B6" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458705</v>
+        <v>459066</v>
       </c>
       <c r="R6" t="n">
-        <v>7073870</v>
+        <v>7073606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815638</v>
+        <v>119815764</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,20 +1217,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459085</v>
+        <v>459148</v>
       </c>
       <c r="R7" t="n">
-        <v>7073606</v>
+        <v>7073462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815340</v>
+        <v>119815610</v>
       </c>
       <c r="B8" t="n">
-        <v>79652</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459110</v>
+        <v>458934</v>
       </c>
       <c r="R8" t="n">
-        <v>7073509</v>
+        <v>7073666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815635</v>
+        <v>119815472</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459066</v>
+        <v>458907</v>
       </c>
       <c r="R9" t="n">
-        <v>7073606</v>
+        <v>7073661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815764</v>
+        <v>119815247</v>
       </c>
       <c r="B10" t="n">
-        <v>79658</v>
+        <v>74654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459148</v>
+        <v>458953</v>
       </c>
       <c r="R10" t="n">
-        <v>7073462</v>
+        <v>7073657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815766</v>
+        <v>119815375</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>97951</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458974</v>
+        <v>458705</v>
       </c>
       <c r="R11" t="n">
-        <v>7073639</v>
+        <v>7073870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815247</v>
+        <v>119815535</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>93958</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>2387</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
         <v>458953</v>
       </c>
       <c r="R12" t="n">
-        <v>7073657</v>
+        <v>7073651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815337</v>
+        <v>119815642</v>
       </c>
       <c r="B13" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458974</v>
+        <v>458927</v>
       </c>
       <c r="R13" t="n">
-        <v>7073639</v>
+        <v>7073670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815472</v>
+        <v>119815247</v>
       </c>
       <c r="B9" t="n">
-        <v>79651</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458907</v>
+        <v>458953</v>
       </c>
       <c r="R9" t="n">
-        <v>7073661</v>
+        <v>7073657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815247</v>
+        <v>119815472</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>79651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458953</v>
+        <v>458907</v>
       </c>
       <c r="R10" t="n">
-        <v>7073657</v>
+        <v>7073661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815535</v>
+        <v>119815642</v>
       </c>
       <c r="B12" t="n">
-        <v>93958</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458953</v>
+        <v>458927</v>
       </c>
       <c r="R12" t="n">
-        <v>7073651</v>
+        <v>7073670</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815642</v>
+        <v>119815535</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>93958</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458927</v>
+        <v>458953</v>
       </c>
       <c r="R13" t="n">
-        <v>7073670</v>
+        <v>7073651</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815766</v>
+        <v>119815535</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>93958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458974</v>
+        <v>458953</v>
       </c>
       <c r="R2" t="n">
-        <v>7073639</v>
+        <v>7073651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815340</v>
+        <v>119815610</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459110</v>
+        <v>458934</v>
       </c>
       <c r="R3" t="n">
-        <v>7073509</v>
+        <v>7073666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815337</v>
+        <v>119815638</v>
       </c>
       <c r="B4" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458974</v>
+        <v>459085</v>
       </c>
       <c r="R4" t="n">
-        <v>7073639</v>
+        <v>7073606</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815638</v>
+        <v>119815642</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459085</v>
+        <v>458927</v>
       </c>
       <c r="R5" t="n">
-        <v>7073606</v>
+        <v>7073670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815764</v>
+        <v>119815337</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459148</v>
+        <v>458974</v>
       </c>
       <c r="R7" t="n">
-        <v>7073462</v>
+        <v>7073639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815610</v>
+        <v>119815375</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>97951</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458934</v>
+        <v>458705</v>
       </c>
       <c r="R8" t="n">
-        <v>7073666</v>
+        <v>7073870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815472</v>
+        <v>119815766</v>
       </c>
       <c r="B10" t="n">
-        <v>79651</v>
+        <v>79658</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458907</v>
+        <v>458974</v>
       </c>
       <c r="R10" t="n">
-        <v>7073661</v>
+        <v>7073639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815375</v>
+        <v>119815340</v>
       </c>
       <c r="B11" t="n">
-        <v>97951</v>
+        <v>79652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458705</v>
+        <v>459110</v>
       </c>
       <c r="R11" t="n">
-        <v>7073870</v>
+        <v>7073509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815642</v>
+        <v>119815472</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458927</v>
+        <v>458907</v>
       </c>
       <c r="R12" t="n">
-        <v>7073670</v>
+        <v>7073661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815535</v>
+        <v>119815764</v>
       </c>
       <c r="B13" t="n">
-        <v>93958</v>
+        <v>79658</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2387</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458953</v>
+        <v>459148</v>
       </c>
       <c r="R13" t="n">
-        <v>7073651</v>
+        <v>7073462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119815535</v>
       </c>
       <c r="B2" t="n">
-        <v>93958</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815610</v>
+        <v>119815635</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458934</v>
+        <v>459066</v>
       </c>
       <c r="R3" t="n">
-        <v>7073666</v>
+        <v>7073606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,16 +880,11 @@
         <v>119815638</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -996,16 +981,11 @@
         <v>119815642</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815635</v>
+        <v>119815247</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459066</v>
+        <v>458953</v>
       </c>
       <c r="R6" t="n">
-        <v>7073606</v>
+        <v>7073657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815337</v>
+        <v>119815472</v>
       </c>
       <c r="B7" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458974</v>
+        <v>458907</v>
       </c>
       <c r="R7" t="n">
-        <v>7073639</v>
+        <v>7073661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815375</v>
+        <v>119815337</v>
       </c>
       <c r="B8" t="n">
-        <v>97951</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458705</v>
+        <v>458974</v>
       </c>
       <c r="R8" t="n">
-        <v>7073870</v>
+        <v>7073639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815247</v>
+        <v>119815340</v>
       </c>
       <c r="B9" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458953</v>
+        <v>459110</v>
       </c>
       <c r="R9" t="n">
-        <v>7073657</v>
+        <v>7073509</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815766</v>
+        <v>119815764</v>
       </c>
       <c r="B10" t="n">
-        <v>79658</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458974</v>
+        <v>459148</v>
       </c>
       <c r="R10" t="n">
-        <v>7073639</v>
+        <v>7073462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815340</v>
+        <v>119815766</v>
       </c>
       <c r="B11" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459110</v>
+        <v>458974</v>
       </c>
       <c r="R11" t="n">
-        <v>7073509</v>
+        <v>7073639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815472</v>
+        <v>119815775</v>
       </c>
       <c r="B12" t="n">
-        <v>79651</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458907</v>
+        <v>458864</v>
       </c>
       <c r="R12" t="n">
-        <v>7073661</v>
+        <v>7073783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119815764</v>
+        <v>119815776</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>219811</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459148</v>
+        <v>458857</v>
       </c>
       <c r="R13" t="n">
-        <v>7073462</v>
+        <v>7073790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,6 +1880,208 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119815375</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fjällflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>458705</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7073870</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119815594</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fjällflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>458834</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7073794</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 24370-2024 artfynd.xlsx
+++ b/artfynd/A 24370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815638</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815247</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815472</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815337</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815340</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815764</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815766</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815775</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815776</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815375</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,8 +2156,29 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>